--- a/data/raw/GLNPO 2024 Spring/Michigan/D100/MI 17 D100 Spring 2024 24GM00I33 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Michigan/D100/MI 17 D100 Spring 2024 24GM00I33 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Michigan\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Michigan\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0C66B4-1E22-4210-ABE6-B4EC3EB874E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E60396-7562-4994-8D59-32AEFED4BCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{70F7823B-CD36-443E-B444-1EA320FB305D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70F7823B-CD36-443E-B444-1EA320FB305D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="30" r:id="rId2"/>
+    <pivotCache cacheId="19" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="82">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -249,9 +249,6 @@
   </si>
   <si>
     <t>MAL</t>
-  </si>
-  <si>
-    <t>CALIM</t>
   </si>
   <si>
     <t>Row Labels</t>
@@ -4111,7 +4108,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CF1CC13-BC53-42A0-876B-1C7DEFDC68CC}" name="PivotTable3" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CF1CC13-BC53-42A0-876B-1C7DEFDC68CC}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Z18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4564,20 +4561,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304064C4-5698-4E68-9F37-A311A87D838E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z192"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4630,9 +4628,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -4683,15 +4681,15 @@
         <v>1</v>
       </c>
       <c r="T2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="U2" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -4742,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U3" t="s">
         <v>19</v>
@@ -4760,12 +4758,12 @@
         <v>65</v>
       </c>
       <c r="Z3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -4831,9 +4829,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -4896,9 +4894,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -4964,9 +4962,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -5029,9 +5027,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -5094,9 +5092,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -5159,9 +5157,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -5224,9 +5222,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -5292,9 +5290,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -5360,9 +5358,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -5431,9 +5429,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -5493,9 +5491,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -5564,9 +5562,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -5632,9 +5630,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -5700,9 +5698,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -5753,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U18">
         <v>221</v>
@@ -5774,9 +5772,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -5827,9 +5825,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -5880,9 +5878,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -5933,18 +5931,18 @@
         <v>1</v>
       </c>
       <c r="T21" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="U21" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="U21" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="V21" s="8">
         <v>0.999</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -5996,15 +5994,15 @@
       </c>
       <c r="T22" s="8"/>
       <c r="U22" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V22" s="8">
         <v>0.998</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -6055,18 +6053,18 @@
         <v>1</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V23" s="8">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -6118,15 +6116,15 @@
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V24" s="8">
         <v>0.996</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -6177,16 +6175,16 @@
         <v>1</v>
       </c>
       <c r="T25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="U25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="U25" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="V25" s="8"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -6237,16 +6235,16 @@
         <v>1</v>
       </c>
       <c r="T26" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="U26" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="U26" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="V26" s="8"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -6297,13 +6295,13 @@
         <v>1</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U27" s="8"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -6354,9 +6352,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -6407,9 +6405,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -6460,9 +6458,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -6513,9 +6511,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -6566,9 +6564,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -6619,9 +6617,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -6672,9 +6670,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -6725,9 +6723,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -6778,9 +6776,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -6831,9 +6829,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -6884,9 +6882,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -6937,9 +6935,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -6990,9 +6988,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -7043,9 +7041,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -7096,9 +7094,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -7149,9 +7147,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -7202,9 +7200,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -7255,9 +7253,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -7308,9 +7306,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -7361,9 +7359,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -7414,9 +7412,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -7467,9 +7465,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -7520,9 +7518,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -7573,9 +7571,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -7626,9 +7624,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -7679,9 +7677,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -7732,9 +7730,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -7785,9 +7783,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -7838,9 +7836,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -7891,9 +7889,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -7944,9 +7942,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -7997,9 +7995,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -8050,9 +8048,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -8103,9 +8101,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -8156,9 +8154,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -8209,9 +8207,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -8262,9 +8260,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -8315,9 +8313,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -8368,9 +8366,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -8421,9 +8419,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -8474,9 +8472,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -8527,9 +8525,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -8580,9 +8578,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -8633,9 +8631,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -8686,9 +8684,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -8739,9 +8737,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -8792,9 +8790,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -8845,9 +8843,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -8898,9 +8896,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -8951,9 +8949,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -9004,9 +9002,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -9057,9 +9055,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -9110,9 +9108,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -9163,9 +9161,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -9216,9 +9214,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -9269,9 +9267,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -9322,9 +9320,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -9375,9 +9373,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -9428,9 +9426,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -9481,9 +9479,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -9534,9 +9532,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -9587,9 +9585,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -9640,9 +9638,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -9693,9 +9691,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -9746,9 +9744,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -9799,9 +9797,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -9852,9 +9850,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -9905,9 +9903,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -9958,9 +9956,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -10011,9 +10009,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -10064,9 +10062,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -10117,9 +10115,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -10170,9 +10168,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -10223,9 +10221,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -10276,9 +10274,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -10329,9 +10327,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -10382,9 +10380,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -10435,9 +10433,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -10488,9 +10486,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -10541,9 +10539,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -10594,9 +10592,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -10647,9 +10645,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -10700,9 +10698,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
@@ -10753,9 +10751,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -10806,9 +10804,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -10859,9 +10857,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -10912,9 +10910,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
@@ -10965,9 +10963,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
@@ -11018,9 +11016,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
@@ -11071,9 +11069,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
@@ -11124,9 +11122,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
@@ -11177,9 +11175,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
@@ -11230,9 +11228,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
@@ -11283,9 +11281,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
@@ -11336,9 +11334,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B123" t="s">
         <v>17</v>
@@ -11389,9 +11387,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -11442,9 +11440,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -11495,9 +11493,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
@@ -11548,9 +11546,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
@@ -11601,9 +11599,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
@@ -11654,9 +11652,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
@@ -11707,9 +11705,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
@@ -11760,9 +11758,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B131" t="s">
         <v>17</v>
@@ -11813,9 +11811,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B132" t="s">
         <v>17</v>
@@ -11866,9 +11864,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B133" t="s">
         <v>17</v>
@@ -11919,9 +11917,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
@@ -11972,9 +11970,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B135" t="s">
         <v>17</v>
@@ -12025,9 +12023,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B136" t="s">
         <v>17</v>
@@ -12078,9 +12076,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B137" t="s">
         <v>17</v>
@@ -12131,9 +12129,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B138" t="s">
         <v>17</v>
@@ -12184,9 +12182,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B139" t="s">
         <v>17</v>
@@ -12237,9 +12235,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B140" t="s">
         <v>17</v>
@@ -12290,9 +12288,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B141" t="s">
         <v>17</v>
@@ -12343,9 +12341,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B142" t="s">
         <v>17</v>
@@ -12396,9 +12394,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B143" t="s">
         <v>17</v>
@@ -12449,9 +12447,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B144" t="s">
         <v>17</v>
@@ -12502,9 +12500,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B145" t="s">
         <v>17</v>
@@ -12555,9 +12553,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B146" t="s">
         <v>17</v>
@@ -12608,9 +12606,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B147" t="s">
         <v>17</v>
@@ -12661,9 +12659,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B148" t="s">
         <v>17</v>
@@ -12714,9 +12712,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B149" t="s">
         <v>17</v>
@@ -12767,9 +12765,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B150" t="s">
         <v>17</v>
@@ -12820,9 +12818,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B151" t="s">
         <v>17</v>
@@ -12873,9 +12871,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B152" t="s">
         <v>17</v>
@@ -12926,9 +12924,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B153" t="s">
         <v>17</v>
@@ -12979,9 +12977,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B154" t="s">
         <v>17</v>
@@ -13032,9 +13030,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B155" t="s">
         <v>17</v>
@@ -13085,9 +13083,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B156" t="s">
         <v>17</v>
@@ -13138,9 +13136,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B157" t="s">
         <v>17</v>
@@ -13191,9 +13189,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B158" t="s">
         <v>17</v>
@@ -13244,9 +13242,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B159" t="s">
         <v>17</v>
@@ -13297,9 +13295,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B160" t="s">
         <v>17</v>
@@ -13350,9 +13348,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B161" t="s">
         <v>17</v>
@@ -13403,9 +13401,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B162" t="s">
         <v>17</v>
@@ -13456,9 +13454,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B163" t="s">
         <v>17</v>
@@ -13509,9 +13507,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B164" t="s">
         <v>17</v>
@@ -13562,9 +13560,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B165" t="s">
         <v>17</v>
@@ -13615,9 +13613,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B166" t="s">
         <v>17</v>
@@ -13668,9 +13666,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B167" t="s">
         <v>17</v>
@@ -13721,9 +13719,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B168" t="s">
         <v>17</v>
@@ -13774,9 +13772,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B169" t="s">
         <v>17</v>
@@ -13827,9 +13825,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B170" t="s">
         <v>17</v>
@@ -13880,9 +13878,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B171" t="s">
         <v>17</v>
@@ -13933,9 +13931,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B172" t="s">
         <v>17</v>
@@ -13986,9 +13984,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B173" t="s">
         <v>17</v>
@@ -14039,9 +14037,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B174" t="s">
         <v>17</v>
@@ -14092,9 +14090,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B175" t="s">
         <v>17</v>
@@ -14145,9 +14143,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B176" t="s">
         <v>17</v>
@@ -14198,9 +14196,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B177" t="s">
         <v>17</v>
@@ -14251,9 +14249,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B178" t="s">
         <v>17</v>
@@ -14304,9 +14302,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>17</v>
@@ -14357,9 +14355,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>17</v>
@@ -14410,9 +14408,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>17</v>
@@ -14463,9 +14461,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>17</v>
@@ -14516,9 +14514,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>17</v>
@@ -14569,9 +14567,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>17</v>
@@ -14622,9 +14620,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>17</v>
@@ -14675,9 +14673,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>17</v>
@@ -14713,7 +14711,7 @@
         <v>56</v>
       </c>
       <c r="M186" s="4" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="N186" s="4" t="s">
         <v>30</v>
@@ -14728,9 +14726,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>17</v>
@@ -14766,7 +14764,7 @@
         <v>56</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="N187" s="4" t="s">
         <v>30</v>
@@ -14781,9 +14779,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>17</v>
@@ -14834,9 +14832,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>17</v>
@@ -14887,9 +14885,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>17</v>
@@ -14940,9 +14938,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>17</v>
@@ -14993,9 +14991,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>17</v>
@@ -15047,7 +15045,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q192" xr:uid="{304064C4-5698-4E68-9F37-A311A87D838E}"/>
+  <autoFilter ref="A1:Q192" xr:uid="{304064C4-5698-4E68-9F37-A311A87D838E}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="CALIM"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/raw/GLNPO 2024 Spring/Michigan/D100/MI 17 D100 Spring 2024 24GM00I33 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Michigan/D100/MI 17 D100 Spring 2024 24GM00I33 Zoop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Michigan\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E60396-7562-4994-8D59-32AEFED4BCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E2C82D-78B4-430B-9479-22C1EEEE3151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70F7823B-CD36-443E-B444-1EA320FB305D}"/>
+    <workbookView xWindow="1800" yWindow="4704" windowWidth="17280" windowHeight="8880" xr2:uid="{70F7823B-CD36-443E-B444-1EA320FB305D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId2"/>
+    <pivotCache cacheId="15" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4108,7 +4108,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CF1CC13-BC53-42A0-876B-1C7DEFDC68CC}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CF1CC13-BC53-42A0-876B-1C7DEFDC68CC}" name="PivotTable3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Z18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -7194,7 +7194,7 @@
         <v>1.08</v>
       </c>
       <c r="P44" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -11175,7 +11175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>81</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>33</v>
       </c>
       <c r="N186" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O186" s="4" t="s">
         <v>35</v>
@@ -14767,7 +14767,7 @@
         <v>33</v>
       </c>
       <c r="N187" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O187" s="4" t="s">
         <v>35</v>
@@ -15046,9 +15046,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q192" xr:uid="{304064C4-5698-4E68-9F37-A311A87D838E}">
-    <filterColumn colId="12">
+    <filterColumn colId="10">
       <filters>
-        <filter val="CALIM"/>
+        <filter val="Limnocalanus copepodites"/>
       </filters>
     </filterColumn>
   </autoFilter>
